--- a/docs/er-crafting-tc.xlsx
+++ b/docs/er-crafting-tc.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="239">
   <si>
     <t xml:space="preserve">Test Report</t>
   </si>
@@ -6751,39 +6751,116 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">확인 필요</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">가나다순과 관계없이 설정한 부위 순서대로 제작되는지</t>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가나다순과 관계없이 설정한 카테고리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">부위 순서대로 제작됨</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">설정 화면 순서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">소모품 → 무기 → 기타 → 방어구</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">옷 → 머리 → 팔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">장식 → 다리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">특수</t>
     </r>
   </si>
   <si>
@@ -7321,7 +7398,26 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">: "                                        "</t>
+      <t xml:space="preserve">: "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">아이템이 충분하지 않습니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">."</t>
     </r>
   </si>
   <si>
@@ -7502,7 +7598,26 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">없음 </t>
+      <t xml:space="preserve">스크린샷 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">장 </t>
     </r>
     <r>
       <rPr>
@@ -7521,7 +7636,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">추후 재현 시 스크린샷 첨부 권장</t>
+      <t xml:space="preserve">게이지 종료 시 안내 문구</t>
     </r>
     <r>
       <rPr>
@@ -7934,7 +8049,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="10">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -7962,14 +8077,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFF2CC"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -8386,7 +8493,7 @@
       </c>
       <c r="B9" s="9" t="n">
         <f aca="false">SUMPRODUCT(ISNUMBER(제작!$A$4:$A$200)*(제작!$I$4:$I$200="Pass"))+SUMPRODUCT(ISNUMBER(제작!$A$4:$A$200)*(제작!$I$4:$I$200="")*(제작!$H$4:$H$200="Pass"))</f>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C9" s="9" t="n">
         <f aca="false">SUMPRODUCT(ISNUMBER(제작!$A$4:$A$200)*(제작!$I$4:$I$200="Fail"))+SUMPRODUCT(ISNUMBER(제작!$A$4:$A$200)*(제작!$I$4:$I$200="")*(제작!$H$4:$H$200="Fail"))</f>
@@ -8402,7 +8509,7 @@
       </c>
       <c r="F9" s="9" t="n">
         <f aca="false">SUMPRODUCT(ISNUMBER(제작!$A$4:$A$200)*(제작!$I$4:$I$200="N/T"))+SUMPRODUCT(ISNUMBER(제작!$A$4:$A$200)*(제작!$I$4:$I$200="")*(제작!$H$4:$H$200="N/T"))+SUMPRODUCT(ISNUMBER(제작!$A$4:$A$200)*(제작!$I$4:$I$200="")*(제작!$H$4:$H$200=""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="9" t="n">
         <f aca="false">SUMPRODUCT(--ISNUMBER(제작!$A$4:$A$200))</f>
@@ -8410,11 +8517,11 @@
       </c>
       <c r="H9" s="10" t="n">
         <f aca="false">IF(G9=0,0,(G9-F9)/G9)</f>
-        <v>0.977272727272727</v>
+        <v>1</v>
       </c>
       <c r="I9" s="10" t="n">
         <f aca="false">IF(G9-E9=0,0,B9/(G9-E9))</f>
-        <v>0.977272727272727</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10028,13 +10135,17 @@
       <c r="F47" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="G47" s="6" t="s">
+      <c r="G47" s="12" t="s">
         <v>211</v>
       </c>
-      <c r="H47" s="18"/>
+      <c r="H47" s="18" t="s">
+        <v>13</v>
+      </c>
       <c r="I47" s="18"/>
       <c r="J47" s="18"/>
-      <c r="K47" s="13"/>
+      <c r="K47" s="12" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="18"/>
@@ -12032,19 +12143,19 @@
     <mergeCell ref="A2:K2"/>
   </mergeCells>
   <conditionalFormatting sqref="H4:I200">
-    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>"Pass"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>"Fail"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>"Block"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>"N/T"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12079,13 +12190,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="15" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B1" s="15"/>
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B3" s="13" t="s">
         <v>191</v>
@@ -12093,50 +12204,50 @@
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12144,52 +12255,52 @@
         <v>38</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="B12" s="5" t="s">
         <v>230</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B17" s="14"/>
     </row>
